--- a/РАБОЧИЙ СТОЛ/ПРОБЛЕМЫ/перемещение СЫРЫ в Крым.xlsx
+++ b/РАБОЧИЙ СТОЛ/ПРОБЛЕМЫ/перемещение СЫРЫ в Крым.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Uaer4\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\РАБОЧИЙ СТОЛ\ПРОБЛЕМЫ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E3AE006-E5EF-4C75-B89F-E0781C2ABDBB}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C145C734-4DAF-4F6C-BE9A-943CE791E065}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
     <sheet name="ИТОГОВЫЕ ДАННЫЕ" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029" refMode="R1C1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -707,7 +707,7 @@
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
